--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325511</v>
+        <v>123325505</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>58341</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600380</v>
+        <v>600394</v>
       </c>
       <c r="R2" t="n">
-        <v>6973433</v>
+        <v>6973397</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1460</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Produktionsskog</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325505</v>
+        <v>123325511</v>
       </c>
       <c r="B3" t="n">
-        <v>58338</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600394</v>
+        <v>600380</v>
       </c>
       <c r="R3" t="n">
-        <v>6973397</v>
+        <v>6973433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1463</t>
+          <t>2024_1460</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>vid myr</t>
+          <t>Produktionsskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -948,7 +948,7 @@
         <v>123325507</v>
       </c>
       <c r="B4" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325505</v>
+        <v>123325507</v>
       </c>
       <c r="B2" t="n">
-        <v>58341</v>
+        <v>78507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600394</v>
+        <v>600360</v>
       </c>
       <c r="R2" t="n">
-        <v>6973397</v>
+        <v>6973421</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1463</t>
+          <t>2024_1462</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>vid myr</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,7 +813,7 @@
         <v>123325511</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325507</v>
+        <v>123325505</v>
       </c>
       <c r="B4" t="n">
-        <v>78505</v>
+        <v>58341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600360</v>
+        <v>600394</v>
       </c>
       <c r="R4" t="n">
-        <v>6973421</v>
+        <v>6973397</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1462</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325507</v>
+        <v>123325511</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600360</v>
+        <v>600380</v>
       </c>
       <c r="R2" t="n">
-        <v>6973421</v>
+        <v>6973433</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1462</t>
+          <t>2024_1460</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>Produktionsskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325511</v>
+        <v>123325507</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600380</v>
+        <v>600360</v>
       </c>
       <c r="R3" t="n">
-        <v>6973433</v>
+        <v>6973421</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1460</t>
+          <t>2024_1462</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Produktionsskog</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325511</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325507</v>
+        <v>123325505</v>
       </c>
       <c r="B3" t="n">
-        <v>78508</v>
+        <v>58341</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600360</v>
+        <v>600394</v>
       </c>
       <c r="R3" t="n">
-        <v>6973421</v>
+        <v>6973397</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1462</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325505</v>
+        <v>123325507</v>
       </c>
       <c r="B4" t="n">
-        <v>58341</v>
+        <v>78511</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600394</v>
+        <v>600360</v>
       </c>
       <c r="R4" t="n">
-        <v>6973397</v>
+        <v>6973421</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1463</t>
+          <t>2024_1462</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>vid myr</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325511</v>
+        <v>123325507</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600380</v>
+        <v>600360</v>
       </c>
       <c r="R2" t="n">
-        <v>6973433</v>
+        <v>6973421</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1460</t>
+          <t>2024_1462</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Produktionsskog</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325505</v>
+        <v>123325511</v>
       </c>
       <c r="B3" t="n">
-        <v>58341</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600394</v>
+        <v>600380</v>
       </c>
       <c r="R3" t="n">
-        <v>6973397</v>
+        <v>6973433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1463</t>
+          <t>2024_1460</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>vid myr</t>
+          <t>Produktionsskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325507</v>
+        <v>123325505</v>
       </c>
       <c r="B4" t="n">
-        <v>78511</v>
+        <v>58347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600360</v>
+        <v>600394</v>
       </c>
       <c r="R4" t="n">
-        <v>6973421</v>
+        <v>6973397</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1462</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325507</v>
+        <v>123325511</v>
       </c>
       <c r="B2" t="n">
-        <v>78517</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600360</v>
+        <v>600380</v>
       </c>
       <c r="R2" t="n">
-        <v>6973421</v>
+        <v>6973433</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1462</t>
+          <t>2024_1460</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>Produktionsskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325511</v>
+        <v>123325507</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600380</v>
+        <v>600360</v>
       </c>
       <c r="R3" t="n">
-        <v>6973433</v>
+        <v>6973421</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1460</t>
+          <t>2024_1462</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Produktionsskog</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -948,7 +948,7 @@
         <v>123325505</v>
       </c>
       <c r="B4" t="n">
-        <v>58347</v>
+        <v>58350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325511</v>
+        <v>123325507</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600380</v>
+        <v>600360</v>
       </c>
       <c r="R2" t="n">
-        <v>6973433</v>
+        <v>6973421</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1460</t>
+          <t>2024_1462</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Produktionsskog</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325507</v>
+        <v>123325505</v>
       </c>
       <c r="B3" t="n">
-        <v>78522</v>
+        <v>58351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600360</v>
+        <v>600394</v>
       </c>
       <c r="R3" t="n">
-        <v>6973421</v>
+        <v>6973397</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1462</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325505</v>
+        <v>123325511</v>
       </c>
       <c r="B4" t="n">
-        <v>58350</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600394</v>
+        <v>600380</v>
       </c>
       <c r="R4" t="n">
-        <v>6973397</v>
+        <v>6973433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1463</t>
+          <t>2024_1460</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>vid myr</t>
+          <t>Produktionsskog</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325507</v>
+        <v>123325505</v>
       </c>
       <c r="B2" t="n">
-        <v>78524</v>
+        <v>58351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600360</v>
+        <v>600394</v>
       </c>
       <c r="R2" t="n">
-        <v>6973421</v>
+        <v>6973397</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1462</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325505</v>
+        <v>123325507</v>
       </c>
       <c r="B3" t="n">
-        <v>58351</v>
+        <v>78524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600394</v>
+        <v>600360</v>
       </c>
       <c r="R3" t="n">
-        <v>6973397</v>
+        <v>6973421</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1463</t>
+          <t>2024_1462</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>vid myr</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325505</v>
+        <v>123325507</v>
       </c>
       <c r="B2" t="n">
-        <v>58351</v>
+        <v>78524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600394</v>
+        <v>600360</v>
       </c>
       <c r="R2" t="n">
-        <v>6973397</v>
+        <v>6973421</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1463</t>
+          <t>2024_1462</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>vid myr</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325507</v>
+        <v>123325505</v>
       </c>
       <c r="B3" t="n">
-        <v>78524</v>
+        <v>58351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600360</v>
+        <v>600394</v>
       </c>
       <c r="R3" t="n">
-        <v>6973421</v>
+        <v>6973397</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1462</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325507</v>
+        <v>123325505</v>
       </c>
       <c r="B2" t="n">
-        <v>78524</v>
+        <v>58351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600360</v>
+        <v>600394</v>
       </c>
       <c r="R2" t="n">
-        <v>6973421</v>
+        <v>6973397</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1462</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325505</v>
+        <v>123325511</v>
       </c>
       <c r="B3" t="n">
-        <v>58351</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600394</v>
+        <v>600380</v>
       </c>
       <c r="R3" t="n">
-        <v>6973397</v>
+        <v>6973433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1463</t>
+          <t>2024_1460</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>vid myr</t>
+          <t>Produktionsskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325511</v>
+        <v>123325507</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,21 +961,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600380</v>
+        <v>600360</v>
       </c>
       <c r="R4" t="n">
-        <v>6973433</v>
+        <v>6973421</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1460</t>
+          <t>2024_1462</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Produktionsskog</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325505</v>
+        <v>123325507</v>
       </c>
       <c r="B2" t="n">
-        <v>58351</v>
+        <v>78524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600394</v>
+        <v>600360</v>
       </c>
       <c r="R2" t="n">
-        <v>6973397</v>
+        <v>6973421</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1463</t>
+          <t>2024_1462</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>vid myr</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325511</v>
+        <v>123325505</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>58351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600380</v>
+        <v>600394</v>
       </c>
       <c r="R3" t="n">
-        <v>6973433</v>
+        <v>6973397</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1460</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Produktionsskog</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325507</v>
+        <v>123325511</v>
       </c>
       <c r="B4" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,21 +961,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600360</v>
+        <v>600380</v>
       </c>
       <c r="R4" t="n">
-        <v>6973421</v>
+        <v>6973433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1462</t>
+          <t>2024_1460</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>Produktionsskog</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6795-2023 artfynd.xlsx
+++ b/artfynd/A 6795-2023 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325505</v>
+        <v>123325511</v>
       </c>
       <c r="B3" t="n">
-        <v>58351</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600394</v>
+        <v>600380</v>
       </c>
       <c r="R3" t="n">
-        <v>6973397</v>
+        <v>6973433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1463</t>
+          <t>2024_1460</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>vid myr</t>
+          <t>Produktionsskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325511</v>
+        <v>123325505</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>58351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600380</v>
+        <v>600394</v>
       </c>
       <c r="R4" t="n">
-        <v>6973433</v>
+        <v>6973397</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1460</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Produktionsskog</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD4" t="b">
